--- a/数据表/Datas/CharacterConfig_角色配置.xlsx
+++ b/数据表/Datas/CharacterConfig_角色配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16040"/>
+    <workbookView windowHeight="16080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -340,10 +340,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
     <font>
@@ -540,7 +545,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -592,18 +597,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -941,82 +934,88 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1025,10 +1024,10 @@
     <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1037,10 +1036,10 @@
     <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1049,10 +1048,10 @@
     <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1061,10 +1060,10 @@
     <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1073,45 +1072,57 @@
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1585,334 +1596,336 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="18.8676470588235" customWidth="1"/>
-    <col min="13" max="13" width="18.2573529411765" customWidth="1"/>
+    <col min="1" max="1" width="10" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17" style="2" customWidth="1"/>
+    <col min="5" max="9" width="10" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17" style="2" customWidth="1"/>
+    <col min="11" max="11" width="15" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18.8676470588235" style="2" customWidth="1"/>
+    <col min="13" max="13" width="18.2573529411765" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:13">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:13">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:13">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:13">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12">
         <v>1001</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="6" t="b">
+      <c r="D5" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="12">
         <v>120</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="12">
         <v>40</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="12">
         <v>14</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="12">
         <v>6</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="12">
         <v>12</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="12">
         <v>1</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="12">
         <v>101</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="12">
         <v>0</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12">
         <v>1002</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="6" t="b">
+      <c r="D6" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="12">
         <v>150</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="12">
         <v>30</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="12">
         <v>12</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="12">
         <v>5</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="12">
         <v>8</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="12">
         <v>1</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="12">
         <v>102</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="12">
         <v>0</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:13">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12">
         <v>1003</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="6" t="b">
+      <c r="D7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="12">
         <v>90</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="12">
         <v>80</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="12">
         <v>6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="12">
         <v>16</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="12">
         <v>10</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="12">
         <v>1</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="12">
         <v>103</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="12">
         <v>0</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:13">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12">
         <v>1004</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="6" t="b">
+      <c r="D8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="12">
         <v>100</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="12">
         <v>50</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="12">
         <v>11</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="12">
         <v>9</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="12">
         <v>16</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="12">
         <v>1</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="12">
         <v>104</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="12">
         <v>0</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="12">
         <v>0</v>
       </c>
     </row>

--- a/数据表/Datas/CharacterConfig_角色配置.xlsx
+++ b/数据表/Datas/CharacterConfig_角色配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -68,6 +68,9 @@
     <t>armorItemId</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -80,6 +83,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>string#ref=TbSpriteConfig</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -90,6 +96,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -103,13 +115,35 @@
     </r>
   </si>
   <si>
-    <t>原型名</t>
-  </si>
-  <si>
-    <t>新存档拥有</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原型名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新存档拥有</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>基础</t>
     </r>
     <r>
@@ -133,6 +167,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>基础</t>
     </r>
     <r>
@@ -155,16 +195,46 @@
     </r>
   </si>
   <si>
-    <t>攻击力</t>
-  </si>
-  <si>
-    <t>魔力</t>
-  </si>
-  <si>
-    <t>速度</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>魔力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>速度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>普通攻击行动</t>
     </r>
     <r>
@@ -179,6 +249,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>唯一技能行动</t>
     </r>
     <r>
@@ -193,6 +269,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>初始武器</t>
     </r>
     <r>
@@ -234,6 +316,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>初始防具</t>
     </r>
     <r>
@@ -271,6 +359,17 @@
         <charset val="134"/>
       </rPr>
       <t>为空</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源配置</t>
     </r>
   </si>
   <si>
@@ -289,6 +388,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -303,6 +408,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -317,6 +428,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -377,12 +494,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
       <charset val="134"/>
@@ -543,6 +654,12 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -937,148 +1054,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1112,16 +1229,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1595,7 +1712,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1606,10 +1723,11 @@
     <col min="11" max="11" width="15" style="2" customWidth="1"/>
     <col min="12" max="12" width="18.8676470588235" style="2" customWidth="1"/>
     <col min="13" max="13" width="18.2573529411765" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="33.2058823529412" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:13">
+    <row r="1" ht="20" customHeight="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1649,137 +1767,147 @@
       <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
+    <row r="2" ht="20" customHeight="1" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="F2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:13">
+    <row r="3" ht="20" customHeight="1" spans="1:14">
       <c r="A3" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M3" s="8" t="s">
-        <v>18</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N3" s="8"/>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:13">
+    <row r="4" ht="20" customHeight="1" spans="1:14">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1" spans="1:13">
+    <row r="5" ht="20" customHeight="1" spans="1:14">
       <c r="A5" s="11"/>
       <c r="B5" s="12">
         <v>1001</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" s="12" t="b">
         <v>1</v>
@@ -1811,14 +1939,17 @@
       <c r="M5" s="12">
         <v>0</v>
       </c>
+      <c r="N5" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:13">
+    <row r="6" ht="20" customHeight="1" spans="1:14">
       <c r="A6" s="11"/>
       <c r="B6" s="12">
         <v>1002</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>33</v>
+      <c r="C6" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="12" t="b">
         <v>1</v>
@@ -1850,14 +1981,17 @@
       <c r="M6" s="12">
         <v>0</v>
       </c>
+      <c r="N6" s="12" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="1:13">
+    <row r="7" ht="20" customHeight="1" spans="1:14">
       <c r="A7" s="11"/>
       <c r="B7" s="12">
         <v>1003</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>34</v>
+      <c r="C7" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="D7" s="12" t="b">
         <v>1</v>
@@ -1889,14 +2023,17 @@
       <c r="M7" s="12">
         <v>0</v>
       </c>
+      <c r="N7" s="12" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="8" ht="20" customHeight="1" spans="1:13">
+    <row r="8" ht="20" customHeight="1" spans="1:14">
       <c r="A8" s="11"/>
       <c r="B8" s="12">
         <v>1004</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>35</v>
+      <c r="C8" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="D8" s="12" t="b">
         <v>1</v>
@@ -1927,6 +2064,9 @@
       </c>
       <c r="M8" s="12">
         <v>0</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/CharacterConfig_角色配置.xlsx
+++ b/数据表/Datas/CharacterConfig_角色配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>##var</t>
   </si>
@@ -374,6 +374,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>角色</t>
     </r>
     <r>
@@ -444,6 +450,226 @@
         <charset val="134"/>
       </rPr>
       <t>4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>13</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
     </r>
   </si>
 </sst>
@@ -1712,8 +1938,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" outlineLevelRow="7"/>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
     <col min="2" max="3" width="10" style="2" customWidth="1"/>
@@ -2069,6 +2295,457 @@
         <v>38</v>
       </c>
     </row>
+    <row r="9" ht="18" spans="1:14">
+      <c r="B9" s="12">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>100</v>
+      </c>
+      <c r="F9" s="12">
+        <v>50</v>
+      </c>
+      <c r="G9" s="12">
+        <v>11</v>
+      </c>
+      <c r="H9" s="12">
+        <v>9</v>
+      </c>
+      <c r="I9" s="12">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12">
+        <v>1</v>
+      </c>
+      <c r="K9" s="12">
+        <v>104</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="12">
+        <v>0</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" ht="18" spans="1:14">
+      <c r="B10" s="12">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>100</v>
+      </c>
+      <c r="F10" s="12">
+        <v>50</v>
+      </c>
+      <c r="G10" s="12">
+        <v>11</v>
+      </c>
+      <c r="H10" s="12">
+        <v>9</v>
+      </c>
+      <c r="I10" s="12">
+        <v>16</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1</v>
+      </c>
+      <c r="K10" s="12">
+        <v>104</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="12">
+        <v>0</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" ht="18" spans="1:14">
+      <c r="B11" s="12">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>100</v>
+      </c>
+      <c r="F11" s="12">
+        <v>50</v>
+      </c>
+      <c r="G11" s="12">
+        <v>11</v>
+      </c>
+      <c r="H11" s="12">
+        <v>9</v>
+      </c>
+      <c r="I11" s="12">
+        <v>16</v>
+      </c>
+      <c r="J11" s="12">
+        <v>1</v>
+      </c>
+      <c r="K11" s="12">
+        <v>104</v>
+      </c>
+      <c r="L11" s="12">
+        <v>0</v>
+      </c>
+      <c r="M11" s="12">
+        <v>0</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" ht="18" spans="1:14">
+      <c r="B12" s="12">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>100</v>
+      </c>
+      <c r="F12" s="12">
+        <v>50</v>
+      </c>
+      <c r="G12" s="12">
+        <v>11</v>
+      </c>
+      <c r="H12" s="12">
+        <v>9</v>
+      </c>
+      <c r="I12" s="12">
+        <v>16</v>
+      </c>
+      <c r="J12" s="12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="12">
+        <v>104</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" ht="18" spans="1:14">
+      <c r="B13" s="12">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>100</v>
+      </c>
+      <c r="F13" s="12">
+        <v>50</v>
+      </c>
+      <c r="G13" s="12">
+        <v>11</v>
+      </c>
+      <c r="H13" s="12">
+        <v>9</v>
+      </c>
+      <c r="I13" s="12">
+        <v>16</v>
+      </c>
+      <c r="J13" s="12">
+        <v>1</v>
+      </c>
+      <c r="K13" s="12">
+        <v>104</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0</v>
+      </c>
+      <c r="N13" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" ht="18" spans="1:14">
+      <c r="B14" s="12">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12">
+        <v>100</v>
+      </c>
+      <c r="F14" s="12">
+        <v>50</v>
+      </c>
+      <c r="G14" s="12">
+        <v>11</v>
+      </c>
+      <c r="H14" s="12">
+        <v>9</v>
+      </c>
+      <c r="I14" s="12">
+        <v>16</v>
+      </c>
+      <c r="J14" s="12">
+        <v>1</v>
+      </c>
+      <c r="K14" s="12">
+        <v>104</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12">
+        <v>0</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" ht="18" spans="1:14">
+      <c r="B15" s="12">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>100</v>
+      </c>
+      <c r="F15" s="12">
+        <v>50</v>
+      </c>
+      <c r="G15" s="12">
+        <v>11</v>
+      </c>
+      <c r="H15" s="12">
+        <v>9</v>
+      </c>
+      <c r="I15" s="12">
+        <v>16</v>
+      </c>
+      <c r="J15" s="12">
+        <v>1</v>
+      </c>
+      <c r="K15" s="12">
+        <v>104</v>
+      </c>
+      <c r="L15" s="12">
+        <v>0</v>
+      </c>
+      <c r="M15" s="12">
+        <v>0</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" ht="18" spans="1:14">
+      <c r="B16" s="12">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
+        <v>100</v>
+      </c>
+      <c r="F16" s="12">
+        <v>50</v>
+      </c>
+      <c r="G16" s="12">
+        <v>11</v>
+      </c>
+      <c r="H16" s="12">
+        <v>9</v>
+      </c>
+      <c r="I16" s="12">
+        <v>16</v>
+      </c>
+      <c r="J16" s="12">
+        <v>1</v>
+      </c>
+      <c r="K16" s="12">
+        <v>104</v>
+      </c>
+      <c r="L16" s="12">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12">
+        <v>0</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" ht="18" spans="2:14">
+      <c r="B17" s="12">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>100</v>
+      </c>
+      <c r="F17" s="12">
+        <v>50</v>
+      </c>
+      <c r="G17" s="12">
+        <v>11</v>
+      </c>
+      <c r="H17" s="12">
+        <v>9</v>
+      </c>
+      <c r="I17" s="12">
+        <v>16</v>
+      </c>
+      <c r="J17" s="12">
+        <v>1</v>
+      </c>
+      <c r="K17" s="12">
+        <v>104</v>
+      </c>
+      <c r="L17" s="12">
+        <v>0</v>
+      </c>
+      <c r="M17" s="12">
+        <v>0</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="2:14">
+      <c r="B18" s="12">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12">
+        <v>100</v>
+      </c>
+      <c r="F18" s="12">
+        <v>50</v>
+      </c>
+      <c r="G18" s="12">
+        <v>11</v>
+      </c>
+      <c r="H18" s="12">
+        <v>9</v>
+      </c>
+      <c r="I18" s="12">
+        <v>16</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1</v>
+      </c>
+      <c r="K18" s="12">
+        <v>104</v>
+      </c>
+      <c r="L18" s="12">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12">
+        <v>0</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="18" spans="2:14">
+      <c r="B19" s="12">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12">
+        <v>100</v>
+      </c>
+      <c r="F19" s="12">
+        <v>50</v>
+      </c>
+      <c r="G19" s="12">
+        <v>11</v>
+      </c>
+      <c r="H19" s="12">
+        <v>9</v>
+      </c>
+      <c r="I19" s="12">
+        <v>16</v>
+      </c>
+      <c r="J19" s="12">
+        <v>1</v>
+      </c>
+      <c r="K19" s="12">
+        <v>104</v>
+      </c>
+      <c r="L19" s="12">
+        <v>0</v>
+      </c>
+      <c r="M19" s="12">
+        <v>0</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
